--- a/sellingReport.xlsx
+++ b/sellingReport.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Tickets sold by " sheetId="1" r:id="rId1"/>
+    <sheet name="Tickets sold by Langenkamp" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -25,7 +25,7 @@
     <t>Ticket fee</t>
   </si>
   <si>
-    <t>Total Amount in Eur</t>
+    <t>Total</t>
   </si>
   <si>
     <t>Die Gewitterschwimmerin</t>
@@ -143,13 +143,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5">

--- a/sellingReport.xlsx
+++ b/sellingReport.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Tickets sold by Langenkamp" sheetId="1" r:id="rId1"/>
+    <sheet name="Tickets sold by PayPal" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -126,13 +126,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -143,13 +143,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -160,13 +160,13 @@
         <v>8</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/sellingReport.xlsx
+++ b/sellingReport.xlsx
@@ -5,27 +5,27 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Tickets sold by PayPal" sheetId="1" r:id="rId1"/>
+    <sheet name="Tickets sold by / verkauft von Langenkamp" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
-  <si>
-    <t>House No.</t>
-  </si>
-  <si>
-    <t>Gig</t>
-  </si>
-  <si>
-    <t>Sold tickets</t>
-  </si>
-  <si>
-    <t>Ticket fee</t>
-  </si>
-  <si>
-    <t>Total</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>HHaus Nr.</t>
+  </si>
+  <si>
+    <t>Lesung</t>
+  </si>
+  <si>
+    <t>verkaufte Tickets</t>
+  </si>
+  <si>
+    <t>Ticket-Preis</t>
+  </si>
+  <si>
+    <t>Gesamt</t>
   </si>
   <si>
     <t>Die Gewitterschwimmerin</t>
@@ -38,6 +38,12 @@
   </si>
   <si>
     <t>Das Birnenfeld</t>
+  </si>
+  <si>
+    <t>Der Test</t>
+  </si>
+  <si>
+    <t>der dritte test</t>
   </si>
 </sst>
 </file>
@@ -81,7 +87,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -126,13 +132,13 @@
         <v>6</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -143,13 +149,13 @@
         <v>7</v>
       </c>
       <c r="C4" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -160,13 +166,47 @@
         <v>8</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>12</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>0</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
